--- a/experiments/nrp_sat_card_exp_results.xlsx
+++ b/experiments/nrp_sat_card_exp_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,30 +447,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -495,19 +485,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07001060000000001</v>
+        <v>0.106524</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0365131</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.106524</v>
-      </c>
-      <c r="I2" t="n">
         <v>10.8</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -528,19 +512,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06988850000000001</v>
+        <v>0.107007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0371189</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.107007</v>
-      </c>
-      <c r="I3" t="n">
         <v>10.8</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,19 +539,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07102650000000001</v>
+        <v>0.10938</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0383534</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.10938</v>
-      </c>
-      <c r="I4" t="n">
         <v>10.8</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -594,19 +566,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06945850000000001</v>
+        <v>0.106094</v>
       </c>
       <c r="G5" t="n">
-        <v>0.036635</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.106094</v>
-      </c>
-      <c r="I5" t="n">
         <v>10.7</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,19 +593,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07028139999999999</v>
+        <v>0.107982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.037701</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.107982</v>
-      </c>
-      <c r="I6" t="n">
         <v>10.8</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,19 +620,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07000869999999999</v>
+        <v>0.106633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0366247</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.106633</v>
-      </c>
-      <c r="I7" t="n">
         <v>10.8</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,19 +647,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0695495</v>
+        <v>0.10611</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0365601</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.10611</v>
-      </c>
-      <c r="I8" t="n">
         <v>10.7</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -726,19 +674,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0698445</v>
+        <v>0.10705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.037205</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.10705</v>
-      </c>
-      <c r="I9" t="n">
         <v>10.8</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -759,19 +701,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07100910000000001</v>
+        <v>0.108433</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0374241</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.108433</v>
-      </c>
-      <c r="I10" t="n">
         <v>10.7</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -792,19 +728,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0696036</v>
+        <v>0.10626</v>
       </c>
       <c r="G11" t="n">
-        <v>0.036656</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.10626</v>
-      </c>
-      <c r="I11" t="n">
         <v>10.7</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -827,19 +757,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07006809</v>
+        <v>0.1071473</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03707913</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1071473</v>
-      </c>
-      <c r="I12" t="n">
         <v>10.76</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,30 +807,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -931,19 +845,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0987603</v>
+        <v>0.144027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0452667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.144027</v>
-      </c>
-      <c r="I2" t="n">
         <v>16.8</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -964,19 +872,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.100749</v>
+        <v>0.145715</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0449665</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.145715</v>
-      </c>
-      <c r="I3" t="n">
         <v>16.7</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,19 +899,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0971588</v>
+        <v>0.14117</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0440111</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.14117</v>
-      </c>
-      <c r="I4" t="n">
         <v>16.7</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1030,19 +926,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0980915</v>
+        <v>0.142114</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0440222</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.142114</v>
-      </c>
-      <c r="I5" t="n">
         <v>16.8</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1063,19 +953,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0989569</v>
+        <v>0.143801</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0448444</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.143801</v>
-      </c>
-      <c r="I6" t="n">
         <v>16.7</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1096,19 +980,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0994543</v>
+        <v>0.14456</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0451059</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.14456</v>
-      </c>
-      <c r="I7" t="n">
         <v>16.7</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1129,19 +1007,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0992628</v>
+        <v>0.144096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0448333</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.144096</v>
-      </c>
-      <c r="I8" t="n">
         <v>16.7</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1162,19 +1034,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0979723</v>
+        <v>0.143702</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04573</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.143702</v>
-      </c>
-      <c r="I9" t="n">
         <v>16.7</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1195,19 +1061,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09741660000000001</v>
+        <v>0.141104</v>
       </c>
       <c r="G10" t="n">
-        <v>0.043687</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.141104</v>
-      </c>
-      <c r="I10" t="n">
         <v>16.7</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1228,19 +1088,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0973398</v>
+        <v>0.141794</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0444539</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.141794</v>
-      </c>
-      <c r="I11" t="n">
         <v>16.7</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1263,19 +1117,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09851623</v>
+        <v>0.1432083</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0446921</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1432083</v>
-      </c>
-      <c r="I12" t="n">
         <v>16.72</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,30 +1167,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1367,19 +1205,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.126339</v>
+        <v>0.174535</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0481958</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.174535</v>
-      </c>
-      <c r="I2" t="n">
         <v>24.6</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1400,19 +1232,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.12769</v>
+        <v>0.176351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0486617</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.176351</v>
-      </c>
-      <c r="I3" t="n">
         <v>24.2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1433,19 +1259,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.129951</v>
+        <v>0.180473</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0505224</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.180473</v>
-      </c>
-      <c r="I4" t="n">
         <v>24.6</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1466,19 +1286,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.133103</v>
+        <v>0.18089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0477876</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.18089</v>
-      </c>
-      <c r="I5" t="n">
         <v>24.2</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1499,19 +1313,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.131039</v>
+        <v>0.18073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0496911</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.18073</v>
-      </c>
-      <c r="I6" t="n">
         <v>24.8</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1532,19 +1340,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.135257</v>
+        <v>0.186298</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0510407</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.186298</v>
-      </c>
-      <c r="I7" t="n">
         <v>24.2</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1565,19 +1367,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.128737</v>
+        <v>0.178404</v>
       </c>
       <c r="G8" t="n">
-        <v>0.049667</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.178404</v>
-      </c>
-      <c r="I8" t="n">
         <v>24.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,19 +1394,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.12783</v>
+        <v>0.17772</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0498899</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.17772</v>
-      </c>
-      <c r="I9" t="n">
         <v>24.6</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,19 +1421,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.130924</v>
+        <v>0.181038</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0501136</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.181038</v>
-      </c>
-      <c r="I10" t="n">
         <v>24.5</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,19 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.133274</v>
+        <v>0.184319</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0510449</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.184319</v>
-      </c>
-      <c r="I11" t="n">
         <v>24.2</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1699,19 +1477,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1304144</v>
+        <v>0.1800758</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04966147</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1800758</v>
-      </c>
-      <c r="I12" t="n">
         <v>24.45</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,30 +1527,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1803,19 +1565,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.159301</v>
+        <v>0.212188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.052887</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.212188</v>
-      </c>
-      <c r="I2" t="n">
         <v>29.3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1836,19 +1592,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.155994</v>
+        <v>0.210627</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0546329</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.210627</v>
-      </c>
-      <c r="I3" t="n">
         <v>29.3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1869,19 +1619,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.159755</v>
+        <v>0.212037</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0522819</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.212037</v>
-      </c>
-      <c r="I4" t="n">
         <v>29.2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1902,19 +1646,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.161734</v>
+        <v>0.216079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0543456</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.216079</v>
-      </c>
-      <c r="I5" t="n">
         <v>29.5</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1935,19 +1673,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.154287</v>
+        <v>0.205467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0511792</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.205467</v>
-      </c>
-      <c r="I6" t="n">
         <v>29</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1968,19 +1700,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.155964</v>
+        <v>0.20793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0519663</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.20793</v>
-      </c>
-      <c r="I7" t="n">
         <v>29.7</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2001,19 +1727,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.163388</v>
+        <v>0.215855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0524677</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.215855</v>
-      </c>
-      <c r="I8" t="n">
         <v>29.8</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2034,19 +1754,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.163394</v>
+        <v>0.219052</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0556584</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.219052</v>
-      </c>
-      <c r="I9" t="n">
         <v>29.7</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2067,19 +1781,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.156548</v>
+        <v>0.210303</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0537551</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.210303</v>
-      </c>
-      <c r="I10" t="n">
         <v>29.3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2100,19 +1808,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.158463</v>
+        <v>0.213247</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0547844</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.213247</v>
-      </c>
-      <c r="I11" t="n">
         <v>29.8</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2135,19 +1837,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1588828</v>
+        <v>0.2122785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05339585</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2122785</v>
-      </c>
-      <c r="I12" t="n">
         <v>29.46</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
